--- a/Employee_Reports_wi48/Noel Jarabe Riego Q0165.xlsx
+++ b/Employee_Reports_wi48/Noel Jarabe Riego Q0165.xlsx
@@ -548,11 +548,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
